--- a/sheets/대금율보/검수/우시조 (남창).xlsx
+++ b/sheets/대금율보/검수/우시조 (남창).xlsx
@@ -3920,8 +3920,7 @@
         <is>
           <t xml:space="preserve">仲
 –
-林∧
-‹</t>
+林∧</t>
         </is>
       </c>
       <c r="S4" s="22"/>
@@ -3948,8 +3947,7 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="G5" s="22"/>
@@ -4083,8 +4081,7 @@
         <is>
           <t xml:space="preserve">林∼
 –
-–ㄴ
-‹</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -4100,8 +4097,7 @@
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -4109,8 +4105,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -4120,8 +4115,7 @@
         <is>
           <t xml:space="preserve">–南
 仲南
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -4272,21 +4266,15 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="E10" s="22"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="I10" s="22"/>
@@ -4298,11 +4286,7 @@
         </is>
       </c>
       <c r="K10" s="22"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="22"/>
       <c r="N10" s="21"/>
       <c r="O10" s="22"/>
@@ -4310,8 +4294,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
@@ -4403,8 +4386,7 @@
         <is>
           <t xml:space="preserve">–И⌇
 仲林ʒ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4436,8 +4418,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–ㄴ
-‹</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4457,8 +4438,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-仲林ʒ
-‹</t>
+仲林ʒ</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -4641,8 +4621,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -4672,8 +4651,7 @@
         <is>
           <t xml:space="preserve">㑣⌇
 –
-㑲)
-‹</t>
+㑲)</t>
         </is>
       </c>
       <c r="O15" s="22"/>

--- a/sheets/대금율보/검수/우시조 (남창).xlsx
+++ b/sheets/대금율보/검수/우시조 (남창).xlsx
@@ -3727,30 +3727,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="16.2" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="95.24" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="131.1" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="131.1" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="131.1" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="131.1" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="131.1" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="131.1" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="131.1" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4258,7 +4258,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="131.1" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4301,7 +4301,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="131.1" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4378,7 +4378,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="131.1" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4449,7 +4449,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="131.1" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4536,7 +4536,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="131.1" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4595,7 +4595,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="131.1" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4666,6 +4666,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="42"/>
 </worksheet>
 </file>